--- a/docs/문화포털_자동화_TC_v2.xlsx
+++ b/docs/문화포털_자동화_TC_v2.xlsx
@@ -12,11 +12,11 @@
     <sheet name="자동화선정" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="추적표" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="API응답필드" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="관찰사항" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="결함·관찰" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">API응답필드!$A$1:$D$28</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">관찰사항!$A$1:$H$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">결함·관찰!$A$1:$I$4</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">자동화선정!$A$1:$I$41</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">추적표!$A$1:$M$32</definedName>
   </definedNames>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="437">
   <si>
     <t xml:space="preserve">문화포털 자동화 테스트 — 요약</t>
   </si>
@@ -6179,6 +6179,28 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">API_DF_001</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동화로 발견한 결함 → 결함 존속 시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">XFAIL</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -6319,19 +6341,36 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">관찰사항 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OBS-003</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-01 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,264</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
     </r>
   </si>
   <si>
@@ -8009,7 +8048,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">cPage / rows</t>
+    <t xml:space="preserve">PageNo / numOfrows</t>
   </si>
   <si>
     <t xml:space="preserve">1 / 10</t>
@@ -8038,7 +8077,58 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한 페이지 결과 수</t>
+      <t xml:space="preserve">한 페이지 결과 수 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대소문자 구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">). </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가이드의 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cPage·rows </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 무시됨</t>
     </r>
   </si>
   <si>
@@ -8551,7 +8641,7 @@
     <t xml:space="preserve">대상</t>
   </si>
   <si>
-    <t xml:space="preserve">관찰 내용</t>
+    <t xml:space="preserve">내용</t>
   </si>
   <si>
     <t xml:space="preserve">재현 방법</t>
@@ -8566,9 +8656,399 @@
     <t xml:space="preserve">상태</t>
   </si>
   <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">period2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">잘못된 날짜 형식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(from=2026-10-01)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">을 오류로 거부하지 않고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기간 조건을 무시한 목록을 정상 코드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(00)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 반환함 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(totalCount 13,519, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기간 밖 항목 포함</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">from=2026-10-01, to=20261028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 호출</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사용자가 잘못된 조건으로 조회한 사실을 모른 채 엉뚱한 결과를 받음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">등록 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">자동화 테스트 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">API-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">형식</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-001 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 회귀 확인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">OBS-001</t>
   </si>
   <si>
+    <t xml:space="preserve">관찰</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">period2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요청</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">공식 사용가이드 예시의 페이징 파라미터 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cPage·rows </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">는 무시되고</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">항상 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">페이지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">건</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">응답 태그와 같은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PageNo·numOfrows(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대소문자 구분</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">만 동작함</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">cPage=2·rows=5 / pageNo=2·numOfRows=5 / PageNo=2·numOfrows=5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">세 가지로 호출해 비교</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">가이드대로 개발하면 페이징이 동작하지 않음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">낮음</t>
+  </si>
+  <si>
+    <t xml:space="preserve">문서 수정 요청 대상</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS-002</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-09-30</t>
   </si>
   <si>
@@ -8594,44 +9074,53 @@
     <r>
       <rPr>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">요청 파라미터는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cPage·rows</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인데 응답 태그는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PageNo·numOfrows</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 이름과 대소문자 표기가 일관되지 않음</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">thumbnail URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가 아닌 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">http</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">로 제공됨</t>
     </r>
   </si>
   <si>
@@ -8659,107 +9148,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">body </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">태그 확인</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">클라이언트가 태그명을 잘못 해석할 가능성 있음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">낮음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">명세 확인 필요</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-002</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">thumbnail URL</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가 아닌 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">http</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 제공됨</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">period2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">정상 호출 후 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">thumbnail </t>
     </r>
     <r>
@@ -8809,90 +9197,6 @@
   </si>
   <si>
     <t xml:space="preserve">확인 필요</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-003</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2019-06-16 ~ 2019-12-31 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">기간 조회 시 결과가 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건뿐임</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">과거 데이터 보관 범위가 명세에 없음</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">from=20190616, to=20191231</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">로 호출</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">과거 기간 조회 결과 부족을 오류로 오인할 수 있음</t>
-  </si>
-  <si>
-    <t xml:space="preserve">정보</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기록</t>
   </si>
 </sst>
 </file>
@@ -11684,7 +11988,7 @@
       </c>
       <c r="M17" s="15"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
         <v>266</v>
       </c>
@@ -11704,7 +12008,7 @@
         <v>56</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>56</v>
+        <v>268</v>
       </c>
       <c r="H18" s="15" t="s">
         <v>56</v>
@@ -11721,23 +12025,25 @@
       <c r="L18" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="M18" s="15"/>
+      <c r="M18" s="16" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F19" s="15" t="s">
         <v>56</v>
@@ -11760,22 +12066,22 @@
       <c r="L19" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>272</v>
+      <c r="M19" s="15" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>219</v>
@@ -11805,16 +12111,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>56</v>
@@ -11844,16 +12150,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>238</v>
@@ -11868,7 +12174,7 @@
         <v>56</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J22" s="15" t="s">
         <v>214</v>
@@ -11880,21 +12186,21 @@
         <v>10</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>238</v>
@@ -11909,7 +12215,7 @@
         <v>56</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J23" s="15" t="s">
         <v>214</v>
@@ -11921,21 +12227,21 @@
         <v>10</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B24" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E24" s="16" t="s">
         <v>238</v>
@@ -11950,7 +12256,7 @@
         <v>56</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J24" s="15" t="s">
         <v>214</v>
@@ -11962,7 +12268,7 @@
         <v>10</v>
       </c>
       <c r="M24" s="16" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11973,10 +12279,10 @@
         <v>12</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>56</v>
@@ -11991,7 +12297,7 @@
         <v>56</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J25" s="15" t="s">
         <v>6</v>
@@ -12006,16 +12312,16 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>211</v>
@@ -12030,7 +12336,7 @@
         <v>56</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J26" s="15" t="s">
         <v>214</v>
@@ -12045,16 +12351,16 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E27" s="15" t="s">
         <v>56</v>
@@ -12069,7 +12375,7 @@
         <v>56</v>
       </c>
       <c r="I27" s="15" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J27" s="15" t="s">
         <v>6</v>
@@ -12084,31 +12390,31 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" s="15" t="s">
         <v>303</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>301</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>214</v>
@@ -12123,16 +12429,16 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E29" s="15" t="s">
         <v>56</v>
@@ -12147,7 +12453,7 @@
         <v>56</v>
       </c>
       <c r="I29" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J29" s="15" t="s">
         <v>6</v>
@@ -12162,31 +12468,31 @@
     </row>
     <row r="30" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="15" t="s">
         <v>309</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>310</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="I30" s="15" t="s">
-        <v>307</v>
       </c>
       <c r="J30" s="15" t="s">
         <v>214</v>
@@ -12201,16 +12507,16 @@
     </row>
     <row r="31" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>219</v>
@@ -12225,7 +12531,7 @@
         <v>56</v>
       </c>
       <c r="I31" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J31" s="15" t="s">
         <v>214</v>
@@ -12246,10 +12552,10 @@
         <v>12</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E32" s="15" t="s">
         <v>56</v>
@@ -12264,7 +12570,7 @@
         <v>56</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>214</v>
@@ -12276,7 +12582,7 @@
         <v>10</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -12317,178 +12623,178 @@
         <v>2</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="16" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>344</v>
-      </c>
       <c r="D9" s="16" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>199</v>
@@ -12496,212 +12802,212 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -12722,125 +13028,137 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="21" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>406</v>
+        <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>413</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="44" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C2" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="16" t="s">
         <v>415</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="E2" s="16" t="s">
         <v>417</v>
       </c>
+      <c r="F2" s="15" t="s">
+        <v>418</v>
+      </c>
       <c r="G2" s="16" t="s">
-        <v>418</v>
-      </c>
-      <c r="H2" s="16" t="s">
         <v>419</v>
       </c>
+      <c r="H2" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>421</v>
+      </c>
     </row>
-    <row r="3" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C3" s="15" t="s">
         <v>414</v>
       </c>
+      <c r="C3" s="16" t="s">
+        <v>423</v>
+      </c>
       <c r="D3" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>422</v>
+        <v>424</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>425</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>424</v>
+        <v>428</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>414</v>
+        <v>431</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>423</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="F4" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>428</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>430</v>
+      <c r="I4" s="16" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:I4"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
